--- a/DAGoPERT_AILV.xlsx
+++ b/DAGoPERT_AILV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djmontage\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elena\Desktop\FH\INNO\AILV-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DB02FF-CC00-4F1F-BFB2-C49464A66713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F1B624-EE21-4850-B8C4-00423438D11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1663,6 +1663,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1695,10 +1699,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -1843,49 +1843,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.4328315577127524</c:v>
+                  <c:v>1.4828622159501934</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4558871969361618</c:v>
+                  <c:v>1.5074068182081237</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4648532788563764</c:v>
+                  <c:v>1.51695194130843</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.469976754239356</c:v>
+                  <c:v>1.5224062973657477</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4754204468337719</c:v>
+                  <c:v>1.528201550676648</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4802237050053155</c:v>
+                  <c:v>1.5333150094803836</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.4888695697140941</c:v>
+                  <c:v>1.5425192353271073</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.496875</c:v>
+                  <c:v>1.5510416666666667</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.504880430285906</c:v>
+                  <c:v>1.5595640980062258</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5135262949946844</c:v>
+                  <c:v>1.5687683238529497</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.518329553166228</c:v>
+                  <c:v>1.5738817826566851</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5237732457606439</c:v>
+                  <c:v>1.5796770359675854</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.5288967211436237</c:v>
+                  <c:v>1.5851313920249033</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.5378628030638384</c:v>
+                  <c:v>1.5946765151252094</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.5609184422872475</c:v>
+                  <c:v>1.6192211173831399</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3208,27 +3208,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="134" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="153" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
-      <c r="L1" s="153"/>
-      <c r="M1" s="153"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="152" t="s">
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="154"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="155"/>
+      <c r="O1" s="153" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="153"/>
-      <c r="Q1" s="154"/>
+      <c r="P1" s="154"/>
+      <c r="Q1" s="155"/>
     </row>
     <row r="2" spans="1:17" s="53" customFormat="1" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A2" s="128" t="s">
@@ -3290,34 +3290,34 @@
       <c r="D3" s="54"/>
       <c r="E3" s="127">
         <f>SUM(E4:E10006)</f>
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F3" s="55">
         <f>SUM(F4:F10006)</f>
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G3" s="55">
         <f>SUM(G4:G10006)</f>
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H3" s="56"/>
       <c r="I3" s="57">
         <f>SUM(I4:I10006)</f>
-        <v>239.5</v>
+        <v>248.16666666666666</v>
       </c>
       <c r="J3" s="58">
         <f>SUM(J4:J10006)</f>
-        <v>239.5</v>
+        <v>248.16666666666666</v>
       </c>
       <c r="K3" s="57"/>
       <c r="L3" s="57"/>
       <c r="M3" s="103">
         <f>N3^(1/2)</f>
-        <v>5.123475382979799</v>
+        <v>5.4543560573178569</v>
       </c>
       <c r="N3" s="121">
         <f>SUM(N4:N10006)</f>
-        <v>26.25</v>
+        <v>29.749999999999996</v>
       </c>
       <c r="O3" s="114"/>
       <c r="P3" s="59"/>
@@ -3759,7 +3759,7 @@
       <c r="G12" s="139">
         <v>6</v>
       </c>
-      <c r="H12" s="162"/>
+      <c r="H12" s="152"/>
       <c r="I12" s="140">
         <f t="shared" si="5"/>
         <v>4.166666666666667</v>
@@ -3864,19 +3864,19 @@
         <v>7</v>
       </c>
       <c r="F14" s="139">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" s="139">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" s="131"/>
       <c r="I14" s="140">
         <f t="shared" si="5"/>
-        <v>9.3333333333333339</v>
+        <v>10.333333333333334</v>
       </c>
       <c r="J14" s="141">
         <f t="shared" si="0"/>
-        <v>9.3333333333333339</v>
+        <v>10.333333333333334</v>
       </c>
       <c r="K14" s="142">
         <v>99.73</v>
@@ -3887,11 +3887,11 @@
       </c>
       <c r="M14" s="144">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="N14" s="145">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.7777777777777777</v>
       </c>
       <c r="O14" s="146" t="str">
         <f t="shared" si="4"/>
@@ -3916,21 +3916,21 @@
         <v>3</v>
       </c>
       <c r="F15" s="139">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="139">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H15" s="151" t="s">
         <v>166</v>
       </c>
       <c r="I15" s="140">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="141">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="142">
         <v>99.73</v>
@@ -3941,11 +3941,11 @@
       </c>
       <c r="M15" s="144">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="N15" s="145">
         <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
+        <v>1</v>
       </c>
       <c r="O15" s="146" t="str">
         <f t="shared" si="4"/>
@@ -3970,19 +3970,19 @@
         <v>4</v>
       </c>
       <c r="F16" s="139">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="139">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="131"/>
       <c r="I16" s="140">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="J16" s="141">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K16" s="142">
         <v>99.73</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="M16" s="144">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="N16" s="145">
         <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
+        <v>0.69444444444444453</v>
       </c>
       <c r="O16" s="146" t="str">
         <f t="shared" si="4"/>
@@ -4019,22 +4019,22 @@
         <v>168</v>
       </c>
       <c r="E17" s="139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="139">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G17" s="139">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H17" s="131"/>
       <c r="I17" s="140">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="J17" s="141">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K17" s="142">
         <v>99.73</v>
@@ -4045,15 +4045,15 @@
       </c>
       <c r="M17" s="144">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="N17" s="145">
         <f t="shared" si="3"/>
-        <v>0.1111111111111111</v>
+        <v>0.69444444444444453</v>
       </c>
       <c r="O17" s="146" t="str">
         <f t="shared" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="P17" s="117"/>
       <c r="Q17" s="118"/>
@@ -4071,19 +4071,19 @@
         <v>10</v>
       </c>
       <c r="F18" s="139">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="139">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H18" s="131"/>
       <c r="I18" s="140">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="141">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="142">
         <v>99.73</v>
@@ -4094,11 +4094,11 @@
       </c>
       <c r="M18" s="144">
         <f t="shared" si="2"/>
-        <v>1.3333333333333333</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="N18" s="145">
         <f t="shared" si="3"/>
-        <v>1.7777777777777777</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="O18" s="146" t="str">
         <f t="shared" si="4"/>
@@ -4123,19 +4123,19 @@
         <v>3</v>
       </c>
       <c r="F19" s="139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="139">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H19" s="131"/>
       <c r="I19" s="140">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="141">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" s="142">
         <v>99.73</v>
@@ -4146,11 +4146,11 @@
       </c>
       <c r="M19" s="144">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N19" s="145">
         <f t="shared" si="3"/>
-        <v>0.1111111111111111</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="O19" s="146" t="str">
         <f t="shared" si="4"/>
@@ -15518,20 +15518,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="157"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="158"/>
     </row>
     <row r="2" spans="1:12" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="160"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="161"/>
       <c r="L2" s="50"/>
     </row>
     <row r="3" spans="1:12" s="8" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15561,19 +15561,19 @@
       </c>
       <c r="B4" s="23">
         <f>IF((Spezifikation!J3-(2*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(2*Spezifikation!M3)))</f>
-        <v>229.25304923404039</v>
+        <v>237.25795455203095</v>
       </c>
       <c r="C4" s="18">
         <f>IF(B4="NV",C5,B4/Einstellungen!$B$53)</f>
-        <v>28.656631154255049</v>
+        <v>29.657244319003869</v>
       </c>
       <c r="D4" s="18">
         <f>IF(B4="NV",D5,B4/Einstellungen!$B$54)</f>
-        <v>1.4328315577127524</v>
+        <v>1.4828622159501934</v>
       </c>
       <c r="E4" s="6">
         <f>IF(B4="NV",E5,B4/Einstellungen!$B$55)</f>
-        <v>0.11940262980939603</v>
+        <v>0.12357185132918279</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -15582,19 +15582,19 @@
       </c>
       <c r="B5" s="23">
         <f>IF((Spezifikation!J3-(1.28*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1.28*Spezifikation!M3)))</f>
-        <v>232.94195150978587</v>
+        <v>241.1850909132998</v>
       </c>
       <c r="C5" s="18">
         <f>IF(B5="NV",C6,B5/Einstellungen!$B$53)</f>
-        <v>29.117743938723233</v>
+        <v>30.148136364162475</v>
       </c>
       <c r="D5" s="18">
         <f>IF(B5="NV",D6,B5/Einstellungen!$B$54)</f>
-        <v>1.4558871969361618</v>
+        <v>1.5074068182081237</v>
       </c>
       <c r="E5" s="6">
         <f>IF(B5="NV",E6,B5/Einstellungen!$B$55)</f>
-        <v>0.12132393307801347</v>
+        <v>0.12561723485067697</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -15603,19 +15603,19 @@
       </c>
       <c r="B6" s="18">
         <f>IF((Spezifikation!J3-(1*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1*Spezifikation!M3)))</f>
-        <v>234.37652461702021</v>
+        <v>242.7123106093488</v>
       </c>
       <c r="C6" s="18">
         <f>IF(B6="NV",C7,B6/Einstellungen!$B$53)</f>
-        <v>29.297065577127526</v>
+        <v>30.339038826168601</v>
       </c>
       <c r="D6" s="18">
         <f>IF(B6="NV",D7,B6/Einstellungen!$B$54)</f>
-        <v>1.4648532788563764</v>
+        <v>1.51695194130843</v>
       </c>
       <c r="E6" s="6">
         <f>IF(B6="NV",E7,B6/Einstellungen!$B$55)</f>
-        <v>0.12207110657136469</v>
+        <v>0.12641266177570251</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -15624,19 +15624,19 @@
       </c>
       <c r="B7" s="18">
         <f>IF((Spezifikation!J3-(0.84*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.84*Spezifikation!M3)))</f>
-        <v>235.19628067829697</v>
+        <v>243.58500757851965</v>
       </c>
       <c r="C7" s="18">
         <f>IF(B7="NV",C8,B7/Einstellungen!$B$53)</f>
-        <v>29.399535084787122</v>
+        <v>30.448125947314956</v>
       </c>
       <c r="D7" s="18">
         <f>IF(B7="NV",D8,B7/Einstellungen!$B$54)</f>
-        <v>1.469976754239356</v>
+        <v>1.5224062973657477</v>
       </c>
       <c r="E7" s="6">
         <f>IF(B7="NV",E8,B7/Einstellungen!$B$55)</f>
-        <v>0.12249806285327967</v>
+        <v>0.12686719144714564</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -15645,19 +15645,19 @@
       </c>
       <c r="B8" s="22">
         <f>IF((Spezifikation!J3-(0.67*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.67*Spezifikation!M3)))</f>
-        <v>236.06727149340352</v>
+        <v>244.51224810826369</v>
       </c>
       <c r="C8" s="22">
         <f>IF(B8="NV",C9,B8/Einstellungen!$B$53)</f>
-        <v>29.508408936675441</v>
+        <v>30.564031013532961</v>
       </c>
       <c r="D8" s="22">
         <f>IF(B8="NV",D9,B8/Einstellungen!$B$54)</f>
-        <v>1.4754204468337719</v>
+        <v>1.528201550676648</v>
       </c>
       <c r="E8" s="22">
         <f>IF(B8="NV",E9,B8/Einstellungen!$B$55)</f>
-        <v>0.12295170390281433</v>
+        <v>0.127350129223054</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -15666,19 +15666,19 @@
       </c>
       <c r="B9" s="18">
         <f>IF((Spezifikation!J3-(0.52*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.52*Spezifikation!M3)))</f>
-        <v>236.8357928008505</v>
+        <v>245.33040151686137</v>
       </c>
       <c r="C9" s="18">
         <f>IF(B9="NV",C10,B9/Einstellungen!$B$53)</f>
-        <v>29.604474100106312</v>
+        <v>30.666300189607671</v>
       </c>
       <c r="D9" s="18">
         <f>IF(B9="NV",D10,B9/Einstellungen!$B$54)</f>
-        <v>1.4802237050053155</v>
+        <v>1.5333150094803836</v>
       </c>
       <c r="E9" s="6">
         <f>IF(B9="NV",E10,B9/Einstellungen!$B$55)</f>
-        <v>0.12335197541710964</v>
+        <v>0.12777625079003196</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -15687,19 +15687,19 @@
       </c>
       <c r="B10" s="18">
         <f>IF((Spezifikation!J3-(0.25*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.25*Spezifikation!M3)))</f>
-        <v>238.21913115425505</v>
+        <v>246.80307765233718</v>
       </c>
       <c r="C10" s="18">
         <f>IF(B10="NV",C11,B10/Einstellungen!$B$53)</f>
-        <v>29.777391394281882</v>
+        <v>30.850384706542147</v>
       </c>
       <c r="D10" s="18">
         <f>IF(B10="NV",D11,B10/Einstellungen!$B$54)</f>
-        <v>1.4888695697140941</v>
+        <v>1.5425192353271073</v>
       </c>
       <c r="E10" s="6">
         <f>IF(B10="NV",E11,B10/Einstellungen!$B$55)</f>
-        <v>0.12407246414284118</v>
+        <v>0.12854326961059229</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -15708,19 +15708,19 @@
       </c>
       <c r="B11" s="22">
         <f>Spezifikation!J3</f>
-        <v>239.5</v>
+        <v>248.16666666666666</v>
       </c>
       <c r="C11" s="22">
         <f>B11/Einstellungen!B53</f>
-        <v>29.9375</v>
+        <v>31.020833333333332</v>
       </c>
       <c r="D11" s="22">
         <f>B11/Einstellungen!B54</f>
-        <v>1.496875</v>
+        <v>1.5510416666666667</v>
       </c>
       <c r="E11" s="135">
         <f>B11/Einstellungen!B55</f>
-        <v>0.12473958333333333</v>
+        <v>0.12925347222222222</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -15729,19 +15729,19 @@
       </c>
       <c r="B12" s="18">
         <f>Spezifikation!J3+(0.25*Spezifikation!M3)</f>
-        <v>240.78086884574495</v>
+        <v>249.53025568099613</v>
       </c>
       <c r="C12" s="18">
         <f>B12/Einstellungen!B53</f>
-        <v>30.097608605718118</v>
+        <v>31.191281960124517</v>
       </c>
       <c r="D12" s="18">
         <f>B12/Einstellungen!B54</f>
-        <v>1.504880430285906</v>
+        <v>1.5595640980062258</v>
       </c>
       <c r="E12" s="6">
         <f>B12/Einstellungen!B55</f>
-        <v>0.12540670252382549</v>
+        <v>0.12996367483385216</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -15750,19 +15750,19 @@
       </c>
       <c r="B13" s="18">
         <f>Spezifikation!J3+(0.52*Spezifikation!M3)</f>
-        <v>242.1642071991495</v>
+        <v>251.00293181647194</v>
       </c>
       <c r="C13" s="18">
         <f>B13/Einstellungen!B53</f>
-        <v>30.270525899893688</v>
+        <v>31.375366477058993</v>
       </c>
       <c r="D13" s="18">
         <f>B13/Einstellungen!B54</f>
-        <v>1.5135262949946844</v>
+        <v>1.5687683238529497</v>
       </c>
       <c r="E13" s="6">
         <f>B13/Einstellungen!B55</f>
-        <v>0.12612719124955704</v>
+        <v>0.13073069365441248</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -15771,19 +15771,19 @@
       </c>
       <c r="B14" s="22">
         <f>Spezifikation!J3+(0.67*Spezifikation!M3)</f>
-        <v>242.93272850659648</v>
+        <v>251.82108522506962</v>
       </c>
       <c r="C14" s="22">
         <f>B14/Einstellungen!B53</f>
-        <v>30.366591063324559</v>
+        <v>31.477635653133703</v>
       </c>
       <c r="D14" s="22">
         <f>B14/Einstellungen!B54</f>
-        <v>1.518329553166228</v>
+        <v>1.5738817826566851</v>
       </c>
       <c r="E14" s="135">
         <f>B14/Einstellungen!B55</f>
-        <v>0.12652746276385232</v>
+        <v>0.13115681522139042</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -15792,19 +15792,19 @@
       </c>
       <c r="B15" s="18">
         <f>Spezifikation!J3+(0.84*Spezifikation!M3)</f>
-        <v>243.80371932170303</v>
+        <v>252.74832575481366</v>
       </c>
       <c r="C15" s="18">
         <f>B15/Einstellungen!B53</f>
-        <v>30.475464915212878</v>
+        <v>31.593540719351708</v>
       </c>
       <c r="D15" s="18">
         <f>B15/Einstellungen!B54</f>
-        <v>1.5237732457606439</v>
+        <v>1.5796770359675854</v>
       </c>
       <c r="E15" s="6">
         <f>B15/Einstellungen!B55</f>
-        <v>0.12698110381338698</v>
+        <v>0.13163975299729877</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -15813,19 +15813,19 @@
       </c>
       <c r="B16" s="18">
         <f>Spezifikation!J3+(1*Spezifikation!M3)</f>
-        <v>244.62347538297979</v>
+        <v>253.62102272398451</v>
       </c>
       <c r="C16" s="18">
         <f>B16/Einstellungen!B53</f>
-        <v>30.577934422872474</v>
+        <v>31.702627840498064</v>
       </c>
       <c r="D16" s="18">
         <f>B16/Einstellungen!B54</f>
-        <v>1.5288967211436237</v>
+        <v>1.5851313920249033</v>
       </c>
       <c r="E16" s="6">
         <f>B16/Einstellungen!B55</f>
-        <v>0.12740806009530198</v>
+        <v>0.13209428266874193</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -15834,19 +15834,19 @@
       </c>
       <c r="B17" s="18">
         <f>Spezifikation!J3+(1.28*Spezifikation!M3)</f>
-        <v>246.05804849021413</v>
+        <v>255.14824242003351</v>
       </c>
       <c r="C17" s="18">
         <f>B17/Einstellungen!B53</f>
-        <v>30.757256061276767</v>
+        <v>31.893530302504189</v>
       </c>
       <c r="D17" s="18">
         <f>B17/Einstellungen!B54</f>
-        <v>1.5378628030638384</v>
+        <v>1.5946765151252094</v>
       </c>
       <c r="E17" s="6">
         <f>B17/Einstellungen!B55</f>
-        <v>0.12815523358865319</v>
+        <v>0.13288970959376745</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -15855,19 +15855,19 @@
       </c>
       <c r="B18" s="26">
         <f>Spezifikation!J3+(2*Spezifikation!M3)</f>
-        <v>249.74695076595961</v>
+        <v>259.07537878130239</v>
       </c>
       <c r="C18" s="26">
         <f>B18/Einstellungen!B53</f>
-        <v>31.218368845744951</v>
+        <v>32.384422347662799</v>
       </c>
       <c r="D18" s="26">
         <f>B18/Einstellungen!B54</f>
-        <v>1.5609184422872475</v>
+        <v>1.6192211173831399</v>
       </c>
       <c r="E18" s="136">
         <f>B18/Einstellungen!B55</f>
-        <v>0.13007653685727064</v>
+        <v>0.13493509311526167</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15905,13 +15905,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="162" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
     </row>
     <row r="2" spans="1:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
@@ -16004,19 +16004,19 @@
       </c>
       <c r="C14" s="32">
         <f>Aufwandschätzung!B8</f>
-        <v>236.06727149340352</v>
+        <v>244.51224810826369</v>
       </c>
       <c r="D14" s="32">
         <f>Aufwandschätzung!B11</f>
-        <v>239.5</v>
+        <v>248.16666666666666</v>
       </c>
       <c r="E14" s="32">
         <f>Aufwandschätzung!B14</f>
-        <v>242.93272850659648</v>
+        <v>251.82108522506962</v>
       </c>
       <c r="F14" s="33">
         <f>Aufwandschätzung!B18</f>
-        <v>249.74695076595961</v>
+        <v>259.07537878130239</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -16025,19 +16025,19 @@
       </c>
       <c r="C15" s="34">
         <f>C14/C6</f>
-        <v>30.658087206935523</v>
+        <v>31.754837416657622</v>
       </c>
       <c r="D15" s="34">
         <f>D14/C6</f>
-        <v>31.103896103896105</v>
+        <v>32.229437229437231</v>
       </c>
       <c r="E15" s="34">
         <f>E14/C6</f>
-        <v>31.549705000856683</v>
+        <v>32.704037042216832</v>
       </c>
       <c r="F15" s="35">
         <f>F14/C6</f>
-        <v>32.434668930644108</v>
+        <v>33.64615308848083</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -16087,19 +16087,19 @@
       </c>
       <c r="C19" s="38">
         <f>(C5*C14)+C16+C17</f>
-        <v>32813.350737583089</v>
+        <v>33987.202487048657</v>
       </c>
       <c r="D19" s="38">
         <f>(C5*D14)+D16+D17</f>
-        <v>33290.5</v>
+        <v>34495.166666666664</v>
       </c>
       <c r="E19" s="38">
         <f>(C5*E14)+E16+E17</f>
-        <v>33767.649262416911</v>
+        <v>35003.130846284679</v>
       </c>
       <c r="F19" s="40">
         <f>(C5*F14)+F16+F17</f>
-        <v>34714.826156468385</v>
+        <v>36011.477650601031</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -16961,18 +16961,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17154,6 +17154,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F155915-390F-4DB1-8323-6D9C71B4FD2C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90C8B9A1-CF49-4753-98D3-CDFF9713AD0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -17165,14 +17173,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F155915-390F-4DB1-8323-6D9C71B4FD2C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
